--- a/docs/mau-du-lieu/mau-danh-muc.xlsx
+++ b/docs/mau-du-lieu/mau-danh-muc.xlsx
@@ -15,24 +15,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="98">
-  <si>
-    <t>KHAI BÁO DANH MỤC — HƯỚNG DẪN</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="101">
+  <si>
+    <t>Mục</t>
+  </si>
+  <si>
+    <t>Bắt buộc</t>
+  </si>
+  <si>
+    <t>Giải thích</t>
+  </si>
+  <si>
+    <t>Vì sao điền file này trước</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Vì sao phải điền file này trước</t>
-  </si>
-  <si>
-    <t>Hồ sơ thiết bị tham chiếu tới site / tủ / loại / nhà cung cấp. Danh mục vào trước thì lúc import 300 thiết bị hệ thống mới đối chiếu được và chặn được lỗi gõ sai.</t>
+    <t>Hồ sơ thiết bị tham chiếu tới site / tủ / loại / nhà cung cấp. Danh mục vào trước thì lúc import thiết bị hệ thống mới đối chiếu được và chặn được lỗi gõ sai.</t>
   </si>
   <si>
     <t>Thứ tự làm</t>
   </si>
   <si>
-    <t>1) Điền 4 sheet trong file này  →  2) Import danh mục  →  3) Điền file mau-import-thiet-bi.xlsx  →  4) Import thiết bị</t>
+    <t>1) Điền 4 sheet trong file này → 2) Quản trị › Danh mục › Nhập từ Excel → 3) Điền file mẫu thiết bị → 4) Import thiết bị</t>
   </si>
   <si>
     <t>Dòng có chữ VÍ DỤ</t>
@@ -44,7 +50,13 @@
     <t>Cột có dấu *</t>
   </si>
   <si>
-    <t>Bắt buộc. Thiếu là dòng đó bị báo lỗi và không được nhập.</t>
+    <t>Bắt buộc. Thiếu là dòng đó báo lỗi và không được nhập.</t>
+  </si>
+  <si>
+    <t>Cột bị xóa khỏi file</t>
+  </si>
+  <si>
+    <t>Bỏ hẳn một cột = "đừng đụng tới trường đó" (giữ nguyên giá trị đang có). Để cột lại nhưng bỏ trống ô = xóa giá trị đó đi.</t>
   </si>
   <si>
     <t>Sheet Site</t>
@@ -53,10 +65,7 @@
     <t>Mã site</t>
   </si>
   <si>
-    <t>Bắt buộc</t>
-  </si>
-  <si>
-    <t>VIẾT HOA, không dấu, không khoảng trắng. Đây là mã anh gõ khi tra cứu, đổi về sau rất phiền — chốt kỹ. Vd: PMH-HO, PMH-NM, PMH-KHO.</t>
+    <t>VIẾT HOA, không dấu, không khoảng trắng. Đây là mã gõ khi tra cứu, đổi về sau rất phiền — chốt kỹ. Vd: PMH-HO, PMH-NM, PMH-KHO.</t>
   </si>
   <si>
     <t>Tên site</t>
@@ -77,7 +86,7 @@
     <t>Thuộc site</t>
   </si>
   <si>
-    <t>Phải khớp một Mã site ở sheet Site.</t>
+    <t>Phải khớp một Mã site ở sheet Site (hoặc site đã có trong hệ thống). Hệ thống KHÔNG tự tạo site mới từ đây.</t>
   </si>
   <si>
     <t>Số U</t>
@@ -86,7 +95,7 @@
     <t>Không</t>
   </si>
   <si>
-    <t>Chiều cao tủ (số U). Bỏ trống nếu không rõ.</t>
+    <t>Chiều cao tủ (số nguyên dương). Bỏ trống nếu không rõ.</t>
   </si>
   <si>
     <t>Thiết bị không nằm trong tủ</t>
@@ -98,7 +107,7 @@
     <t>Sheet Loại thiết bị</t>
   </si>
   <si>
-    <t>Đã điền sẵn 12 loại</t>
+    <t>Có sẵn 12 loại</t>
   </si>
   <si>
     <t>Sửa/xóa/thêm thoải mái. Loại nào công ty không có thì xóa cho gọn danh sách chọn.</t>
@@ -119,7 +128,7 @@
     <t>Tên nhà cung cấp</t>
   </si>
   <si>
-    <t>Ghi đúng tên hay dùng khi liên hệ bảo hành. Trùng tên sẽ bị gộp.</t>
+    <t>Ghi đúng tên hay dùng khi liên hệ bảo hành. Trùng tên sẽ được coi là cùng một NCC.</t>
   </si>
   <si>
     <t>Điện thoại / liên hệ</t>
@@ -131,7 +140,7 @@
     <t>Sau khi điền xong</t>
   </si>
   <si>
-    <t>Vào màn Quản trị › Danh mục › Import, chọn file này. Hệ thống hiện bảng đối chiếu (thêm mới / cập nhật / lỗi) để anh duyệt TRƯỚC khi ghi.</t>
+    <t>Vào Quản trị › Danh mục › Nhập từ Excel, chọn file này. Hệ thống hiện bảng đối chiếu (thêm mới / cập nhật / lỗi) để duyệt TRƯỚC khi ghi.</t>
   </si>
   <si>
     <t>Import lại lần nữa</t>
@@ -315,17 +324,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
     </font>
     <font>
       <b/>
@@ -355,23 +360,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -716,304 +710,304 @@
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="96" style="1" customWidth="1"/>
+    <col min="3" max="3" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1030,49 +1024,49 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="6" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>48</v>
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1090,75 +1084,75 @@
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2">
+        <v>42</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="7">
-        <v>42</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="7">
-        <v>42</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="2">
         <v>24</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>48</v>
+      <c r="E4" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1176,189 +1170,189 @@
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>44</v>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1377,58 +1371,58 @@
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="6" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>48</v>
+      <c r="D2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
